--- a/input/PL/reg_leave_parental_home.xlsx
+++ b/input/PL/reg_leave_parental_home.xlsx
@@ -15,211 +15,154 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="80" uniqueCount="46">
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Authors:</t>
+  </si>
+  <si>
+    <t>Last edit:</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Process:</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Modelparametersgoverningleavi</t>
+  </si>
+  <si>
+    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
+    <t>12 Jan 2016 AB</t>
+  </si>
   <si>
     <t>Description:</t>
   </si>
   <si>
-    <t>Model parameters governing leaving parental home process</t>
-  </si>
-  <si>
-    <t>Authors:</t>
-  </si>
-  <si>
-    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
-  </si>
-  <si>
-    <t>Last edit:</t>
-  </si>
-  <si>
-    <t>12 Jan 2016 AB</t>
-  </si>
-  <si>
-    <t>Process:</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
     <t>Probit regression estimates for leaving the parental home, transitioning out of adult child status</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>Regions: PL4 = Polnocno-Zachodni, PL5 = Poludniowo-Zachodni, PL6 = Polnocy, PL10 = Central + East. Poludniowy is the omitted category.</t>
-  </si>
-  <si>
     <t>DV is synchronised with the adult child definition</t>
   </si>
   <si>
-    <t>Goodness of fit</t>
+    <t>Goodnessoffit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 - Leaving the parental home </t>
+  </si>
+  <si>
+    <t>Pseudo R-squared</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Chi^2</t>
+  </si>
+  <si>
+    <t>Log likelihood</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>REGRESSOR</t>
   </si>
   <si>
+    <t>Dgn</t>
+  </si>
+  <si>
+    <t>Dag</t>
+  </si>
+  <si>
+    <t>Dag_sq</t>
+  </si>
+  <si>
+    <t>Deh_c4_Medium_L1</t>
+  </si>
+  <si>
+    <t>Deh_c4_Low_L1</t>
+  </si>
+  <si>
+    <t>Les_c3_Student_L1</t>
+  </si>
+  <si>
+    <t>Les_c3_NotEmployed_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q2_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q3_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q4_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q5_L1</t>
+  </si>
+  <si>
+    <t>PL4</t>
+  </si>
+  <si>
+    <t>PL5</t>
+  </si>
+  <si>
+    <t>PL6</t>
+  </si>
+  <si>
+    <t>PL10</t>
+  </si>
+  <si>
+    <t>Year_transformed</t>
+  </si>
+  <si>
+    <t>Year_transformed_sq</t>
+  </si>
+  <si>
+    <t>Y2016</t>
+  </si>
+  <si>
+    <t>Y2018</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
     <t>COEFFICIENT</t>
-  </si>
-  <si>
-    <t>Dgn</t>
-  </si>
-  <si>
-    <t>Dag</t>
-  </si>
-  <si>
-    <t>Dag_sq</t>
-  </si>
-  <si>
-    <t>Deh_c4_Medium_L1</t>
-  </si>
-  <si>
-    <t>Deh_c4_Low_L1</t>
-  </si>
-  <si>
-    <t>Les_c3_Student_L1</t>
-  </si>
-  <si>
-    <t>Les_c3_NotEmployed_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q2_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q3_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q4_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q5_L1</t>
-  </si>
-  <si>
-    <t>PL4</t>
-  </si>
-  <si>
-    <t>PL5</t>
-  </si>
-  <si>
-    <t>PL6</t>
-  </si>
-  <si>
-    <t>PL10</t>
-  </si>
-  <si>
-    <t>Year_transformed</t>
-  </si>
-  <si>
-    <t>Year_transformed_sq</t>
-  </si>
-  <si>
-    <t>Y2016</t>
-  </si>
-  <si>
-    <t>Y2018</t>
-  </si>
-  <si>
-    <t>Constant</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">P1 - Leaving the parental home </t>
-  </si>
-  <si>
-    <t>Pseudo R-squared</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Chi^2</t>
-  </si>
-  <si>
-    <t>Log likelihood</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="17">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -230,7 +173,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -238,100 +181,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -345,51 +202,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
+      <c r="A11" t="s">
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -402,40 +299,90 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>36</v>
-      </c>
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1">
         <v>0.12973681263102865</v>
       </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
       <c r="E5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1">
         <v>685.66149079710112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1">
         <v>23841</v>
       </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
       <c r="E6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1">
         <v>-5372585.0913683791</v>
       </c>
     </row>
@@ -445,1437 +392,1434 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="M1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="N1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="Q1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="R1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="U1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="V1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1">
         <v>-0.12923783908089082</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.0015165076641799197</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-7.3637442579721962e-05</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>1.0413486415757349e-06</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>-0.00039988177608027317</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-0.00042385589819712713</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>6.7795221754410906e-05</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>-5.5164078446948308e-06</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>0.00014961209439270584</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0.00038654173979777985</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>0.0001532176557645988</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>-7.8027612936309906e-05</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>-1.8709469578298795e-05</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>-0.00010977774506499088</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>3.5133224585038913e-06</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>2.1462358467816569e-05</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>-7.5563085153259167e-05</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>2.4601341197408829e-06</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>0.00017488807374461664</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-3.2926304428793822e-05</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>0.0010254125178361568</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.029030535481083107</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-7.3637442579721962e-05</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.0011938168937831116</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-2.0079304717196722e-05</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>0.00024392969656391542</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>0.00054480444354804754</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>0.001290880812392101</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>0.00053572912598713347</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-0.00015294349436116832</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0.00022835005719789312</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>0.0001932303219480719</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>0.00020938710616336727</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>-0.0002406036896230706</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-5.9096255846535816e-05</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>-7.1000240366571879e-05</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>-8.8401119521812094e-05</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>0.00013014868796527206</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-3.7334118044919006e-06</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-0.00038501649353737564</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>3.3329640870586111e-05</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>-0.018613355637031113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1">
         <v>0.0018337483684336597</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>1.0413486415757349e-06</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-2.0079304717196722e-05</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>3.4172206162393276e-07</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>-3.8762767149661009e-06</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>-9.0757952406033662e-06</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>-2.0045683182405954e-05</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-8.616178165123212e-06</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>2.4308326297062258e-06</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-3.68285036389325e-06</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>-3.2805736969724513e-06</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-3.4621064798937245e-06</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>3.7228410624713715e-06</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>7.0087780931326138e-07</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>9.9450698328265065e-07</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>1.3309489087138897e-06</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>-1.9148792721605122e-06</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>5.3897254459665846e-08</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>5.3082276612572275e-06</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>-6.0689026681434353e-07</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>0.0003077866748547386</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.07265074639618474</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>-0.00039988177608027317</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0.00024392969656391542</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>-3.8762767149661009e-06</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.0020902181271743006</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.0015315323306551774</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>0.00094493860590311955</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>2.9927772365070894e-05</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-0.00014443538088952079</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>-5.6214087932653198e-05</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>0.0001255243528586709</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>0.00036851298045501783</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-0.0001675931296195887</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-6.5330856122797546e-05</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>-0.00018659338157312559</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-6.8698225648290402e-06</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>2.898679915758315e-05</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>-1.0973657996642187e-06</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>0.00011531951044029052</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>0.00010893378641691615</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>-0.0051803351365140252</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.16344245749374711</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-0.00042385589819712713</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>0.00054480444354804754</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>-9.0757952406033662e-06</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.0015315323306551774</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.0045490092398154597</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>6.2263813954630161e-05</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-0.00069939293040339676</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-9.3713762583935169e-05</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>-0.00044021000186899727</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>-0.00012247113053964189</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-7.1293283580946103e-05</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>-0.00032445013676804876</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>2.979021820013431e-05</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>-0.00025546237578167268</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>-0.00012190132809266339</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>-6.3845363312228266e-05</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>7.1630467224945653e-07</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>-0.00024951643124086938</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>0.0003860240924181621</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>-0.0078369723768779136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1">
         <v>-0.3115571085635741</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>6.7795221754410906e-05</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>0.001290880812392101</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-2.0045683182405954e-05</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>0.00094493860590311955</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>6.2263813954630161e-05</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>0.010453254290307825</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>0.006076404118501094</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>-0.00022960069111717016</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0.0050599039797865602</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>0.0060247993298549931</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>0.0060131718896593326</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>-0.00011211827726810911</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>-8.3425213107876216e-05</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>-0.00015733392320616582</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>-0.00021099064539988781</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>0.00044972822758633383</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-1.4488219601118066e-05</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>-0.0010052323361775164</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>-0.00027413454267646766</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>-0.030096585561831792</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.23310835683683032</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>-5.5164078446948308e-06</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>0.00053572912598713347</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-8.616178165123212e-06</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>2.9927772365070894e-05</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-0.00069939293040339676</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>0.006076404118501094</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.007526206018348575</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>-5.5771208592176116e-05</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0.0053773250779842246</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>0.0065020547309643847</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>0.0064237256594333655</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>-0.00029208473627273816</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-0.00016146270759586951</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>-0.00019898859453515758</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-0.00010179242252232785</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>-0.00012952636397264654</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>4.0462235499025154e-06</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-0.00027331575555727657</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>-7.5321426293943009e-05</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>-0.013609529396313583</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.0033887692891730087</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.00014961209439270584</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-0.00015294349436116832</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>2.4308326297062258e-06</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-0.00014443538088952079</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-9.3713762583935169e-05</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>-0.00022960069111717016</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>-5.5771208592176116e-05</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.0045941284404198909</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0.002236879861130814</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>0.0022323565072249873</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>0.0022234908673399454</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>9.100399720439234e-05</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>6.4346352065406569e-05</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>0.0001723597494769663</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>0.00011261686869444906</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>-7.2215109282781703e-05</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>1.6045308452333546e-06</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-3.9998156727261884e-05</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>5.7354603660590719e-05</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>0.00074884418103399186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1">
         <v>-0.094039119662290047</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>0.00038654173979777985</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>0.00022835005719789312</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-3.68285036389325e-06</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>-5.6214087932653198e-05</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>-0.00044021000186899727</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>0.0050599039797865602</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>0.0053773250779842246</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>0.002236879861130814</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0078353084241325529</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>0.0071564541336313573</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>0.0070645508665802895</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>-0.00028638906157907914</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>-3.5491338718531863e-05</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>-6.9004728053366976e-05</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>5.5899646887453368e-05</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>-0.00025196405444716068</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>6.7137911441202694e-06</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>-8.2576596355576903e-05</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>-6.6301266626326866e-05</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>-0.0086213350687294292</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1">
         <v>-0.13690093010580073</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>0.0001532176557645988</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>0.0001932303219480719</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>-3.2805736969724513e-06</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>0.0001255243528586709</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>-0.00012247113053964189</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>0.0060247993298549931</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>0.0065020547309643847</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>0.0022323565072249873</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.0071564541336313573</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.0093841534699309857</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.0082275146154201229</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>-0.00010226691072790222</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>9.0555082884386613e-05</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-1.3522352742460103e-05</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-8.7932975128297429e-06</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-0.00011225866480358052</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>2.1057121711943731e-06</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-3.8299431877690179e-05</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>-1.2600176255032468e-05</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>-0.010125265910763247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1">
         <v>-0.060334875283848732</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>-7.8027612936309906e-05</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>0.00020938710616336727</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-3.4621064798937245e-06</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>0.00036851298045501783</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>-7.1293283580946103e-05</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>0.0060131718896593326</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>0.0064237256594333655</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>0.0022234908673399454</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.0070645508665802895</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>0.0082275146154201229</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.010159434172548396</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>-0.00021865043317681292</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>-0.00016210731299940015</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>-1.2390158404631299e-06</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>2.2876293329268443e-05</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-0.00023999837322971401</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>5.8946247896234479e-06</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-0.00017863575704466991</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>0.0002971440796883263</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>-0.0093632482585353904</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1">
         <v>-0.050712624510217713</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>-1.8709469578298795e-05</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-0.0002406036896230706</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>3.7228410624713715e-06</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-0.0001675931296195887</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-0.00032445013676804876</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>-0.00011211827726810911</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>-0.00029208473627273816</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>9.100399720439234e-05</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>-0.00028638906157907914</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>-0.00010226691072790222</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>-0.00021865043317681292</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.0038109110355206469</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>0.0015180254784944219</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>0.0015434344857026458</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>0.0015340638161944473</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>-0.00013004710407264045</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>3.7423509797487298e-06</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>0.00082329620104574044</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>3.1523102038480194e-05</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>0.003565790779974497</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1">
         <v>-0.031100305964373662</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>-0.00010977774506499088</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-5.9096255846535816e-05</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>7.0087780931326138e-07</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-6.5330856122797546e-05</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>2.979021820013431e-05</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>-8.3425213107876216e-05</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-0.00016146270759586951</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>6.4346352065406569e-05</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>-3.5491338718531863e-05</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>9.0555082884386613e-05</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>-0.00016210731299940015</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>0.0015180254784944219</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.0054096017308457754</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>0.0015049946050930277</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>0.0015329308049645439</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>-0.00030232150452468671</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>7.6203675106747558e-06</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>0.0001474497301240629</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>0.00028624088152951247</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>0.0024950842578870601</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1">
         <v>0.0062870071912579225</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>3.5133224585038913e-06</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-7.1000240366571879e-05</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>9.9450698328265065e-07</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-0.00018659338157312559</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>-0.00025546237578167268</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>-0.00015733392320616582</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>-0.00019898859453515758</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>0.0001723597494769663</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>-6.9004728053366976e-05</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-1.3522352742460103e-05</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>-1.2390158404631299e-06</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>0.0015434344857026458</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>0.0015049946050930277</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.0037760286033435334</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>0.0015337333032985627</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>-2.7409464683883936e-05</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>2.3654612263131144e-07</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>5.7373237627201764e-05</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>0.00027169224295472267</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>0.00019841497278004863</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1">
         <v>0.011174728152921578</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>2.1462358467816569e-05</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>-8.8401119521812094e-05</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>1.3309489087138897e-06</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-6.8698225648290402e-06</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>-0.00012190132809266339</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-0.00021099064539988781</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-0.00010179242252232785</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>0.00011261686869444906</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>5.5899646887453368e-05</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-8.7932975128297429e-06</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>2.2876293329268443e-05</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>0.0015340638161944473</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>0.0015329308049645439</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>0.0015337333032985627</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.0024102767632512619</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>-0.00010206767960711029</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>3.1634963008281776e-06</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>0.00020020903256004097</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>0.00012383849759699023</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>0.00063862215668532827</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.17184525380037741</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>-7.5563085153259167e-05</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>0.00013014868796527206</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>-1.9148792721605122e-06</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>2.898679915758315e-05</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>-6.3845363312228266e-05</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>0.00044972822758633383</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>-0.00012952636397264654</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>-7.2215109282781703e-05</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>-0.00025196405444716068</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-0.00011225866480358052</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-0.00023999837322971401</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>-0.00013004710407264045</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-0.00030232150452468671</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>-2.7409464683883936e-05</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>-0.00010206767960711029</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.0033012111706319388</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>-9.6524001762416018e-05</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>-0.0014617260373677061</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-0.0014821603743967412</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>-0.028465818491881761</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18">
+        <v>41</v>
+      </c>
+      <c r="B18" s="1">
         <v>-0.0053819024631334873</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>2.4601341197408829e-06</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-3.7334118044919006e-06</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>5.3897254459665846e-08</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>-1.0973657996642187e-06</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>7.1630467224945653e-07</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-1.4488219601118066e-05</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>4.0462235499025154e-06</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>1.6045308452333546e-06</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>6.7137911441202694e-06</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>2.1057121711943731e-06</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>5.8946247896234479e-06</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>3.7423509797487298e-06</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>7.6203675106747558e-06</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>2.3654612263131144e-07</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>3.1634963008281776e-06</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>-9.6524001762416018e-05</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>2.8439739532710438e-06</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>4.3518672565811148e-05</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>4.2363676658341569e-05</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>0.00082702087348353261</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1">
         <v>-0.40141685789088594</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>0.00017488807374461664</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-0.00038501649353737564</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>5.3082276612572275e-06</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>0.00011531951044029052</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>-0.00024951643124086938</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>-0.0010052323361775164</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-0.00027331575555727657</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-3.9998156727261884e-05</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>-8.2576596355576903e-05</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-3.8299431877690179e-05</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-0.00017863575704466991</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>0.00082329620104574044</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>0.0001474497301240629</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>5.7373237627201764e-05</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>0.00020020903256004097</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>-0.0014617260373677061</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>4.3518672565811148e-05</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.009669216118983387</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>0.00098629631482627508</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>0.017514393967939041</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20">
+        <v>43</v>
+      </c>
+      <c r="B20" s="1">
         <v>0.38133825288901718</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-3.2926304428793822e-05</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>3.3329640870586111e-05</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>-6.0689026681434353e-07</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>0.00010893378641691615</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>0.0003860240924181621</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>-0.00027413454267646766</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-7.5321426293943009e-05</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>5.7354603660590719e-05</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>-6.6301266626326866e-05</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-1.2600176255032468e-05</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>0.0002971440796883263</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>3.1523102038480194e-05</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>0.00028624088152951247</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>0.00027169224295472267</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>0.00012383849759699023</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-0.0014821603743967412</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>4.2363676658341569e-05</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>0.00098629631482627508</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.0041411279877091364</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>0.011194892078493845</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21">
+        <v>44</v>
+      </c>
+      <c r="B21" s="1">
         <v>-3.310159039252301</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>0.0010254125178361568</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-0.018613355637031113</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>0.0003077866748547386</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>-0.0051803351365140252</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>-0.0078369723768779136</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>-0.030096585561831792</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>-0.013609529396313583</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>0.00074884418103399186</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>-0.0086213350687294292</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>-0.010125265910763247</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>-0.0093632482585353904</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>0.003565790779974497</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>0.0024950842578870601</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>0.00019841497278004863</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>0.00063862215668532827</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>-0.028465818491881761</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>0.00082702087348353261</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>0.017514393967939041</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>0.011194892078493845</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.51739465812123631</v>
       </c>
     </row>
